--- a/data/usdc-deribit.xlsx
+++ b/data/usdc-deribit.xlsx
@@ -5,39 +5,29 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\marti\Desktop\azure-projects\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\marti\Desktop\azure-projects\tax-project-new\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:9_{847978B8-52BB-491E-85EE-22958FFEF249}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{592D0CA6-A623-4CE0-8DF8-99FE8E82B59C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{98526837-788E-4274-A536-05D25C8F2C63}"/>
+    <workbookView xWindow="3930" yWindow="3930" windowWidth="21600" windowHeight="11295" xr2:uid="{821DB695-47A5-423E-917F-6ED5ADF38B8E}"/>
   </bookViews>
   <sheets>
     <sheet name="usdc-deribit" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="62">
   <si>
     <t>ID</t>
   </si>
   <si>
+    <t>UserSeq</t>
+  </si>
+  <si>
     <t>Date</t>
   </si>
   <si>
@@ -101,6 +91,9 @@
     <t>Order ID</t>
   </si>
   <si>
+    <t>Info</t>
+  </si>
+  <si>
     <t>Note</t>
   </si>
   <si>
@@ -113,6 +106,9 @@
     <t>null</t>
   </si>
   <si>
+    <t>UPL: 0 RPL: 0.02497879</t>
+  </si>
+  <si>
     <t>SOL_USDC-16MAY25-136-P</t>
   </si>
   <si>
@@ -122,6 +118,27 @@
     <t>close buy</t>
   </si>
   <si>
+    <t>UPL: 0.0752869 RPL: 0</t>
+  </si>
+  <si>
+    <t>UPL: 1.88582235 RPL: 0</t>
+  </si>
+  <si>
+    <t>UPL: -0.23888501 RPL: 0</t>
+  </si>
+  <si>
+    <t>UPL: 1.2194087 RPL: 0</t>
+  </si>
+  <si>
+    <t>UPL: 0.35012205 RPL: 0</t>
+  </si>
+  <si>
+    <t>UPL: 1.3759183 RPL: 0</t>
+  </si>
+  <si>
+    <t>UPL: 4.30734793 RPL: -38.5381269</t>
+  </si>
+  <si>
     <t>ETH_USDC</t>
   </si>
   <si>
@@ -137,6 +154,9 @@
     <t>ETH_USDC-3534468335</t>
   </si>
   <si>
+    <t>Source: mobile</t>
+  </si>
+  <si>
     <t>SOL_USDC-16MAY25-164-C</t>
   </si>
   <si>
@@ -164,6 +184,9 @@
     <t>USDC-33712982095</t>
   </si>
   <si>
+    <t>UPL: -2.4618731 RPL: 0</t>
+  </si>
+  <si>
     <t>USDC-27924871</t>
   </si>
   <si>
@@ -183,9 +206,6 @@
   </si>
   <si>
     <t>ETH_USDC-3513380162</t>
-  </si>
-  <si>
-    <t>RESULT</t>
   </si>
 </sst>
 </file>
@@ -193,7 +213,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd;@"/>
+    <numFmt numFmtId="166" formatCode="yyyy\-mm\-dd;@"/>
   </numFmts>
   <fonts count="18" x14ac:knownFonts="1">
     <font>
@@ -674,7 +694,7 @@
   </cellStyleXfs>
   <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="42">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -1049,42 +1069,21 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4C661C29-C3F6-420C-9C08-E6D1F366EA9D}">
-  <dimension ref="A1:X18"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{705EF622-B952-46E4-ACA9-6E5375C1FF1C}">
+  <dimension ref="A1:Y18"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="9" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="24.28515625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="27.42578125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="9.28515625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="7.85546875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="12.5703125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="8.28515625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="7" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="12" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="10.5703125" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="15.140625" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="10" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="8.140625" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="8.28515625" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="11.7109375" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="11.5703125" bestFit="1" customWidth="1"/>
-    <col min="18" max="19" width="11.7109375" bestFit="1" customWidth="1"/>
-    <col min="20" max="21" width="12" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="17.85546875" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="20.85546875" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="5.140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="23.5703125" style="1" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D1" t="s">
@@ -1130,42 +1129,45 @@
         <v>16</v>
       </c>
       <c r="R1" t="s">
-        <v>50</v>
+        <v>17</v>
       </c>
       <c r="S1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="T1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="U1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="V1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="W1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="X1" t="s">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="Y1" t="s">
+        <v>24</v>
       </c>
     </row>
-    <row r="2" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>72483329</v>
       </c>
-      <c r="B2" s="1">
+      <c r="B2">
+        <v>1747382401935620</v>
+      </c>
+      <c r="C2" s="1">
         <v>45793.333333333336</v>
       </c>
-      <c r="D2" t="s">
-        <v>23</v>
-      </c>
       <c r="E2" t="s">
-        <v>24</v>
-      </c>
-      <c r="H2">
-        <v>0</v>
+        <v>25</v>
+      </c>
+      <c r="F2" t="s">
+        <v>26</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -1182,20 +1184,19 @@
       <c r="M2">
         <v>0</v>
       </c>
-      <c r="N2" t="s">
-        <v>25</v>
+      <c r="N2">
+        <v>0</v>
       </c>
       <c r="O2" t="s">
-        <v>24</v>
-      </c>
-      <c r="P2">
-        <v>0</v>
+        <v>27</v>
+      </c>
+      <c r="P2" t="s">
+        <v>26</v>
       </c>
       <c r="Q2">
         <v>0</v>
       </c>
       <c r="R2">
-        <f t="shared" ref="R2:R11" si="0">SUM(M2-P2)</f>
         <v>0</v>
       </c>
       <c r="S2">
@@ -1207,50 +1208,53 @@
       <c r="U2">
         <v>35.612056299999999</v>
       </c>
+      <c r="X2" t="s">
+        <v>28</v>
+      </c>
     </row>
-    <row r="3" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>72481171</v>
       </c>
-      <c r="B3" s="1">
+      <c r="B3">
+        <v>1747382401986730</v>
+      </c>
+      <c r="C3" s="1">
         <v>45793.333333333336</v>
       </c>
-      <c r="C3" t="s">
-        <v>26</v>
-      </c>
       <c r="D3" t="s">
+        <v>29</v>
+      </c>
+      <c r="E3" t="s">
+        <v>30</v>
+      </c>
+      <c r="F3" t="s">
+        <v>31</v>
+      </c>
+      <c r="G3">
+        <v>10</v>
+      </c>
+      <c r="I3">
+        <v>0</v>
+      </c>
+      <c r="J3">
+        <v>0</v>
+      </c>
+      <c r="K3">
+        <v>0</v>
+      </c>
+      <c r="L3">
+        <v>172.1917</v>
+      </c>
+      <c r="M3">
+        <v>172.4117</v>
+      </c>
+      <c r="N3">
+        <v>0</v>
+      </c>
+      <c r="O3" t="s">
         <v>27</v>
       </c>
-      <c r="E3" t="s">
-        <v>28</v>
-      </c>
-      <c r="F3">
-        <v>10</v>
-      </c>
-      <c r="H3">
-        <v>0</v>
-      </c>
-      <c r="I3">
-        <v>0</v>
-      </c>
-      <c r="J3">
-        <v>0</v>
-      </c>
-      <c r="K3">
-        <v>172.1917</v>
-      </c>
-      <c r="L3">
-        <v>172.4117</v>
-      </c>
-      <c r="M3">
-        <v>0</v>
-      </c>
-      <c r="N3" t="s">
-        <v>25</v>
-      </c>
-      <c r="O3">
-        <v>0</v>
-      </c>
       <c r="P3">
         <v>0</v>
       </c>
@@ -1258,7 +1262,6 @@
         <v>0</v>
       </c>
       <c r="R3">
-        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="S3">
@@ -1271,21 +1274,21 @@
         <v>35.612056299999999</v>
       </c>
     </row>
-    <row r="4" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>72303110</v>
       </c>
-      <c r="B4" s="1">
+      <c r="B4">
+        <v>1747296001922800</v>
+      </c>
+      <c r="C4" s="1">
         <v>45792.333333333336</v>
       </c>
-      <c r="D4" t="s">
-        <v>23</v>
-      </c>
       <c r="E4" t="s">
-        <v>24</v>
-      </c>
-      <c r="H4">
-        <v>0</v>
+        <v>25</v>
+      </c>
+      <c r="F4" t="s">
+        <v>26</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -1302,20 +1305,19 @@
       <c r="M4">
         <v>0</v>
       </c>
-      <c r="N4" t="s">
-        <v>25</v>
+      <c r="N4">
+        <v>0</v>
       </c>
       <c r="O4" t="s">
-        <v>24</v>
-      </c>
-      <c r="P4">
-        <v>0</v>
+        <v>27</v>
+      </c>
+      <c r="P4" t="s">
+        <v>26</v>
       </c>
       <c r="Q4">
         <v>0</v>
       </c>
       <c r="R4">
-        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="S4">
@@ -1327,22 +1329,25 @@
       <c r="U4">
         <v>35.58707751</v>
       </c>
+      <c r="X4" t="s">
+        <v>32</v>
+      </c>
     </row>
-    <row r="5" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>72164979</v>
       </c>
-      <c r="B5" s="1">
+      <c r="B5">
+        <v>1747209601838980</v>
+      </c>
+      <c r="C5" s="1">
         <v>45791.333333333336</v>
       </c>
-      <c r="D5" t="s">
-        <v>23</v>
-      </c>
       <c r="E5" t="s">
-        <v>24</v>
-      </c>
-      <c r="H5">
-        <v>0</v>
+        <v>25</v>
+      </c>
+      <c r="F5" t="s">
+        <v>26</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -1359,20 +1364,19 @@
       <c r="M5">
         <v>0</v>
       </c>
-      <c r="N5" t="s">
-        <v>25</v>
+      <c r="N5">
+        <v>0</v>
       </c>
       <c r="O5" t="s">
-        <v>24</v>
-      </c>
-      <c r="P5">
-        <v>0</v>
+        <v>27</v>
+      </c>
+      <c r="P5" t="s">
+        <v>26</v>
       </c>
       <c r="Q5">
         <v>0</v>
       </c>
       <c r="R5">
-        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="S5">
@@ -1384,22 +1388,25 @@
       <c r="U5">
         <v>35.511790609999998</v>
       </c>
+      <c r="X5" t="s">
+        <v>33</v>
+      </c>
     </row>
-    <row r="6" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>72003314</v>
       </c>
-      <c r="B6" s="1">
+      <c r="B6">
+        <v>1747123201956280</v>
+      </c>
+      <c r="C6" s="1">
         <v>45790.333333333336</v>
       </c>
-      <c r="D6" t="s">
-        <v>23</v>
-      </c>
       <c r="E6" t="s">
-        <v>24</v>
-      </c>
-      <c r="H6">
-        <v>0</v>
+        <v>25</v>
+      </c>
+      <c r="F6" t="s">
+        <v>26</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -1416,20 +1423,19 @@
       <c r="M6">
         <v>0</v>
       </c>
-      <c r="N6" t="s">
-        <v>25</v>
+      <c r="N6">
+        <v>0</v>
       </c>
       <c r="O6" t="s">
-        <v>24</v>
-      </c>
-      <c r="P6">
-        <v>0</v>
+        <v>27</v>
+      </c>
+      <c r="P6" t="s">
+        <v>26</v>
       </c>
       <c r="Q6">
         <v>0</v>
       </c>
       <c r="R6">
-        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="S6">
@@ -1441,22 +1447,25 @@
       <c r="U6">
         <v>33.625968270000001</v>
       </c>
+      <c r="X6" t="s">
+        <v>34</v>
+      </c>
     </row>
-    <row r="7" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>71818489</v>
       </c>
-      <c r="B7" s="1">
+      <c r="B7">
+        <v>1747036801899410</v>
+      </c>
+      <c r="C7" s="1">
         <v>45789.333333333336</v>
       </c>
-      <c r="D7" t="s">
-        <v>23</v>
-      </c>
       <c r="E7" t="s">
-        <v>24</v>
-      </c>
-      <c r="H7">
-        <v>0</v>
+        <v>25</v>
+      </c>
+      <c r="F7" t="s">
+        <v>26</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -1473,20 +1482,19 @@
       <c r="M7">
         <v>0</v>
       </c>
-      <c r="N7" t="s">
-        <v>25</v>
+      <c r="N7">
+        <v>0</v>
       </c>
       <c r="O7" t="s">
-        <v>24</v>
-      </c>
-      <c r="P7">
-        <v>0</v>
+        <v>27</v>
+      </c>
+      <c r="P7" t="s">
+        <v>26</v>
       </c>
       <c r="Q7">
         <v>0</v>
       </c>
       <c r="R7">
-        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="S7">
@@ -1498,22 +1506,25 @@
       <c r="U7">
         <v>33.864853279999998</v>
       </c>
+      <c r="X7" t="s">
+        <v>35</v>
+      </c>
     </row>
-    <row r="8" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>71672338</v>
       </c>
-      <c r="B8" s="1">
+      <c r="B8">
+        <v>1746950401913580</v>
+      </c>
+      <c r="C8" s="1">
         <v>45788.333333333336</v>
       </c>
-      <c r="D8" t="s">
-        <v>23</v>
-      </c>
       <c r="E8" t="s">
-        <v>24</v>
-      </c>
-      <c r="H8">
-        <v>0</v>
+        <v>25</v>
+      </c>
+      <c r="F8" t="s">
+        <v>26</v>
       </c>
       <c r="I8">
         <v>0</v>
@@ -1530,20 +1541,19 @@
       <c r="M8">
         <v>0</v>
       </c>
-      <c r="N8" t="s">
-        <v>25</v>
+      <c r="N8">
+        <v>0</v>
       </c>
       <c r="O8" t="s">
-        <v>24</v>
-      </c>
-      <c r="P8">
-        <v>0</v>
+        <v>27</v>
+      </c>
+      <c r="P8" t="s">
+        <v>26</v>
       </c>
       <c r="Q8">
         <v>0</v>
       </c>
       <c r="R8">
-        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="S8">
@@ -1555,22 +1565,25 @@
       <c r="U8">
         <v>32.645444580000003</v>
       </c>
+      <c r="X8" t="s">
+        <v>36</v>
+      </c>
     </row>
-    <row r="9" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>71462807</v>
       </c>
-      <c r="B9" s="1">
+      <c r="B9">
+        <v>1746864001815950</v>
+      </c>
+      <c r="C9" s="1">
         <v>45787.333333333336</v>
       </c>
-      <c r="D9" t="s">
-        <v>23</v>
-      </c>
       <c r="E9" t="s">
-        <v>24</v>
-      </c>
-      <c r="H9">
-        <v>0</v>
+        <v>25</v>
+      </c>
+      <c r="F9" t="s">
+        <v>26</v>
       </c>
       <c r="I9">
         <v>0</v>
@@ -1587,20 +1600,19 @@
       <c r="M9">
         <v>0</v>
       </c>
-      <c r="N9" t="s">
-        <v>25</v>
+      <c r="N9">
+        <v>0</v>
       </c>
       <c r="O9" t="s">
-        <v>24</v>
-      </c>
-      <c r="P9">
-        <v>0</v>
+        <v>27</v>
+      </c>
+      <c r="P9" t="s">
+        <v>26</v>
       </c>
       <c r="Q9">
         <v>0</v>
       </c>
       <c r="R9">
-        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="S9">
@@ -1612,22 +1624,25 @@
       <c r="U9">
         <v>32.29532253</v>
       </c>
+      <c r="X9" t="s">
+        <v>37</v>
+      </c>
     </row>
-    <row r="10" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>71292055</v>
       </c>
-      <c r="B10" s="1">
+      <c r="B10">
+        <v>1746777601986910</v>
+      </c>
+      <c r="C10" s="1">
         <v>45786.333333333336</v>
       </c>
-      <c r="D10" t="s">
-        <v>23</v>
-      </c>
       <c r="E10" t="s">
-        <v>24</v>
-      </c>
-      <c r="H10">
-        <v>0</v>
+        <v>25</v>
+      </c>
+      <c r="F10" t="s">
+        <v>26</v>
       </c>
       <c r="I10">
         <v>0</v>
@@ -1644,20 +1659,19 @@
       <c r="M10">
         <v>0</v>
       </c>
-      <c r="N10" t="s">
-        <v>25</v>
+      <c r="N10">
+        <v>0</v>
       </c>
       <c r="O10" t="s">
-        <v>24</v>
-      </c>
-      <c r="P10">
-        <v>0</v>
+        <v>27</v>
+      </c>
+      <c r="P10" t="s">
+        <v>26</v>
       </c>
       <c r="Q10">
         <v>0</v>
       </c>
       <c r="R10">
-        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="S10">
@@ -1669,47 +1683,50 @@
       <c r="U10">
         <v>30.919404230000001</v>
       </c>
+      <c r="X10" t="s">
+        <v>38</v>
+      </c>
     </row>
-    <row r="11" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>71264598</v>
       </c>
-      <c r="B11" s="1">
+      <c r="B11">
+        <v>1746769760307620</v>
+      </c>
+      <c r="C11" s="1">
         <v>45786.242592592593</v>
       </c>
-      <c r="C11" t="s">
-        <v>29</v>
-      </c>
       <c r="D11" t="s">
-        <v>30</v>
+        <v>39</v>
       </c>
       <c r="E11" t="s">
-        <v>31</v>
-      </c>
-      <c r="F11">
+        <v>40</v>
+      </c>
+      <c r="F11" t="s">
+        <v>41</v>
+      </c>
+      <c r="G11">
         <v>663.51</v>
       </c>
-      <c r="H11">
-        <v>0</v>
-      </c>
       <c r="I11">
+        <v>0</v>
+      </c>
+      <c r="J11">
         <v>2211.6999999999998</v>
-      </c>
-      <c r="J11">
-        <v>2211.5635000000002</v>
       </c>
       <c r="K11">
         <v>2211.5635000000002</v>
       </c>
       <c r="L11">
-        <v>0</v>
+        <v>2211.5635000000002</v>
       </c>
       <c r="M11">
+        <v>0</v>
+      </c>
+      <c r="N11">
         <v>-663.51</v>
       </c>
-      <c r="N11">
-        <v>0</v>
-      </c>
       <c r="O11">
         <v>0</v>
       </c>
@@ -1720,8 +1737,7 @@
         <v>0</v>
       </c>
       <c r="R11">
-        <f t="shared" si="0"/>
-        <v>-663.51</v>
+        <v>0</v>
       </c>
       <c r="S11">
         <v>-663.51</v>
@@ -1733,64 +1749,66 @@
         <v>30.705634440000001</v>
       </c>
       <c r="V11" t="s">
-        <v>32</v>
+        <v>42</v>
       </c>
       <c r="W11" t="s">
-        <v>33</v>
+        <v>43</v>
+      </c>
+      <c r="X11" t="s">
+        <v>44</v>
       </c>
     </row>
-    <row r="12" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>71168954</v>
       </c>
-      <c r="B12" s="1">
+      <c r="B12">
+        <v>1746719032337640</v>
+      </c>
+      <c r="C12" s="1">
         <v>45785.655462962961</v>
       </c>
-      <c r="C12" t="s">
-        <v>34</v>
-      </c>
       <c r="D12" t="s">
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="E12" t="s">
-        <v>28</v>
-      </c>
-      <c r="F12">
+        <v>40</v>
+      </c>
+      <c r="F12" t="s">
+        <v>31</v>
+      </c>
+      <c r="G12">
         <v>10</v>
       </c>
-      <c r="H12">
-        <v>0</v>
-      </c>
       <c r="I12">
+        <v>0</v>
+      </c>
+      <c r="J12">
         <v>6.6</v>
       </c>
-      <c r="J12">
+      <c r="K12">
         <v>6.4019044685010797</v>
       </c>
-      <c r="K12">
+      <c r="L12">
         <v>162.4409</v>
       </c>
-      <c r="L12">
-        <v>0</v>
-      </c>
       <c r="M12">
+        <v>0</v>
+      </c>
+      <c r="N12">
         <v>-66</v>
       </c>
-      <c r="N12">
-        <v>0</v>
-      </c>
       <c r="O12">
+        <v>0</v>
+      </c>
+      <c r="P12">
         <v>5.0000000000000001E-4</v>
       </c>
-      <c r="P12">
+      <c r="Q12">
         <v>0.8122045</v>
       </c>
-      <c r="Q12">
-        <v>0</v>
-      </c>
       <c r="R12">
-        <f>SUM(M12-P12)</f>
-        <v>-66.812204500000007</v>
+        <v>0</v>
       </c>
       <c r="S12">
         <v>-66.812204500000007</v>
@@ -1802,64 +1820,66 @@
         <v>693.67155121999997</v>
       </c>
       <c r="V12" t="s">
-        <v>35</v>
+        <v>46</v>
       </c>
       <c r="W12" t="s">
-        <v>36</v>
+        <v>47</v>
+      </c>
+      <c r="X12" t="s">
+        <v>44</v>
       </c>
     </row>
-    <row r="13" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>71132814</v>
       </c>
-      <c r="B13" s="1">
+      <c r="B13">
+        <v>1746709145526660</v>
+      </c>
+      <c r="C13" s="1">
         <v>45785.541030092594</v>
       </c>
-      <c r="C13" t="s">
-        <v>26</v>
-      </c>
       <c r="D13" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E13" t="s">
-        <v>37</v>
-      </c>
-      <c r="F13">
+        <v>40</v>
+      </c>
+      <c r="F13" t="s">
+        <v>48</v>
+      </c>
+      <c r="G13">
         <v>10</v>
       </c>
-      <c r="H13">
+      <c r="I13">
         <v>-1</v>
       </c>
-      <c r="I13">
+      <c r="J13">
         <v>0.9</v>
       </c>
-      <c r="J13">
+      <c r="K13">
         <v>0.95719152242827399</v>
       </c>
-      <c r="K13">
+      <c r="L13">
         <v>154.58340000000001</v>
       </c>
-      <c r="L13">
-        <v>0</v>
-      </c>
       <c r="M13">
+        <v>0</v>
+      </c>
+      <c r="N13">
         <v>9</v>
       </c>
-      <c r="N13">
-        <v>0</v>
-      </c>
       <c r="O13">
+        <v>0</v>
+      </c>
+      <c r="P13">
         <v>5.0000000000000001E-4</v>
       </c>
-      <c r="P13">
+      <c r="Q13">
         <v>0.77291699999999997</v>
       </c>
-      <c r="Q13">
-        <v>0</v>
-      </c>
       <c r="R13">
-        <f t="shared" ref="R13:R18" si="1">SUM(M13-P13)</f>
-        <v>8.2270830000000004</v>
+        <v>0</v>
       </c>
       <c r="S13">
         <v>8.2270830000000004</v>
@@ -1871,64 +1891,66 @@
         <v>726.01063818</v>
       </c>
       <c r="V13" t="s">
-        <v>38</v>
+        <v>49</v>
       </c>
       <c r="W13" t="s">
-        <v>39</v>
+        <v>50</v>
+      </c>
+      <c r="X13" t="s">
+        <v>44</v>
       </c>
     </row>
-    <row r="14" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>71132408</v>
       </c>
-      <c r="B14" s="1">
+      <c r="B14">
+        <v>1746708596582580</v>
+      </c>
+      <c r="C14" s="1">
         <v>45785.534675925926</v>
       </c>
-      <c r="C14" t="s">
+      <c r="D14" t="s">
+        <v>51</v>
+      </c>
+      <c r="E14" t="s">
         <v>40</v>
       </c>
-      <c r="D14" t="s">
-        <v>30</v>
-      </c>
-      <c r="E14" t="s">
-        <v>28</v>
-      </c>
-      <c r="F14">
+      <c r="F14" t="s">
+        <v>31</v>
+      </c>
+      <c r="G14">
         <v>10</v>
       </c>
-      <c r="H14">
-        <v>0</v>
-      </c>
       <c r="I14">
+        <v>0</v>
+      </c>
+      <c r="J14">
         <v>0.8</v>
       </c>
-      <c r="J14">
+      <c r="K14">
         <v>0.72505890724007305</v>
       </c>
-      <c r="K14">
+      <c r="L14">
         <v>155.18020000000001</v>
       </c>
-      <c r="L14">
-        <v>0</v>
-      </c>
       <c r="M14">
+        <v>0</v>
+      </c>
+      <c r="N14">
         <v>-8</v>
       </c>
-      <c r="N14">
-        <v>0</v>
-      </c>
       <c r="O14">
+        <v>0</v>
+      </c>
+      <c r="P14">
         <v>1E-4</v>
       </c>
-      <c r="P14">
+      <c r="Q14">
         <v>0.15518019999999999</v>
       </c>
-      <c r="Q14">
-        <v>0</v>
-      </c>
       <c r="R14">
-        <f t="shared" si="1"/>
-        <v>-8.1551802000000002</v>
+        <v>0</v>
       </c>
       <c r="S14">
         <v>-8.1551802000000002</v>
@@ -1940,27 +1962,30 @@
         <v>725.12835513000005</v>
       </c>
       <c r="V14" t="s">
-        <v>41</v>
+        <v>52</v>
       </c>
       <c r="W14" t="s">
-        <v>42</v>
+        <v>53</v>
+      </c>
+      <c r="X14" t="s">
+        <v>44</v>
       </c>
     </row>
-    <row r="15" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>71097520</v>
       </c>
-      <c r="B15" s="1">
+      <c r="B15">
+        <v>1746691201704540</v>
+      </c>
+      <c r="C15" s="1">
         <v>45785.333333333336</v>
       </c>
-      <c r="D15" t="s">
-        <v>23</v>
-      </c>
       <c r="E15" t="s">
-        <v>24</v>
-      </c>
-      <c r="H15">
-        <v>0</v>
+        <v>25</v>
+      </c>
+      <c r="F15" t="s">
+        <v>26</v>
       </c>
       <c r="I15">
         <v>0</v>
@@ -1977,20 +2002,19 @@
       <c r="M15">
         <v>0</v>
       </c>
-      <c r="N15" t="s">
-        <v>25</v>
+      <c r="N15">
+        <v>0</v>
       </c>
       <c r="O15" t="s">
-        <v>24</v>
-      </c>
-      <c r="P15">
-        <v>0</v>
+        <v>27</v>
+      </c>
+      <c r="P15" t="s">
+        <v>26</v>
       </c>
       <c r="Q15">
         <v>0</v>
       </c>
       <c r="R15">
-        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="S15">
@@ -2002,59 +2026,61 @@
       <c r="U15">
         <v>730.40048490000004</v>
       </c>
+      <c r="X15" t="s">
+        <v>54</v>
+      </c>
     </row>
-    <row r="16" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>71067235</v>
       </c>
-      <c r="B16" s="1">
+      <c r="B16">
+        <v>1746671419930780</v>
+      </c>
+      <c r="C16" s="1">
         <v>45785.104386574072</v>
       </c>
-      <c r="C16" t="s">
-        <v>34</v>
-      </c>
       <c r="D16" t="s">
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="E16" t="s">
-        <v>37</v>
-      </c>
-      <c r="F16">
+        <v>40</v>
+      </c>
+      <c r="F16" t="s">
+        <v>48</v>
+      </c>
+      <c r="G16">
         <v>10</v>
       </c>
-      <c r="H16">
+      <c r="I16">
         <v>-1</v>
       </c>
-      <c r="I16">
+      <c r="J16">
         <v>1.8</v>
       </c>
-      <c r="J16">
+      <c r="K16">
         <v>1.8735452474243699</v>
       </c>
-      <c r="K16">
+      <c r="L16">
         <v>150.01820000000001</v>
       </c>
-      <c r="L16">
-        <v>0</v>
-      </c>
       <c r="M16">
+        <v>0</v>
+      </c>
+      <c r="N16">
         <v>18</v>
       </c>
-      <c r="N16">
-        <v>0</v>
-      </c>
       <c r="O16">
+        <v>0</v>
+      </c>
+      <c r="P16">
         <v>1E-4</v>
       </c>
-      <c r="P16">
+      <c r="Q16">
         <v>0.15001819999999999</v>
       </c>
-      <c r="Q16">
-        <v>0</v>
-      </c>
       <c r="R16">
-        <f t="shared" si="1"/>
-        <v>17.849981799999998</v>
+        <v>0</v>
       </c>
       <c r="S16">
         <v>17.849981799999998</v>
@@ -2066,64 +2092,66 @@
         <v>737.53746559000001</v>
       </c>
       <c r="V16" t="s">
-        <v>43</v>
+        <v>55</v>
       </c>
       <c r="W16" t="s">
+        <v>56</v>
+      </c>
+      <c r="X16" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="17" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>70988708</v>
       </c>
-      <c r="B17" s="1">
+      <c r="B17">
+        <v>1746610807721640</v>
+      </c>
+      <c r="C17" s="1">
         <v>45784.402858796297</v>
       </c>
-      <c r="C17" t="s">
+      <c r="D17" t="s">
+        <v>51</v>
+      </c>
+      <c r="E17" t="s">
         <v>40</v>
       </c>
-      <c r="D17" t="s">
-        <v>30</v>
-      </c>
-      <c r="E17" t="s">
-        <v>37</v>
-      </c>
-      <c r="F17">
+      <c r="F17" t="s">
+        <v>48</v>
+      </c>
+      <c r="G17">
         <v>10</v>
       </c>
-      <c r="H17">
+      <c r="I17">
         <v>-1</v>
       </c>
-      <c r="I17">
+      <c r="J17">
         <v>1.5</v>
       </c>
-      <c r="J17">
+      <c r="K17">
         <v>1.4166861809208799</v>
       </c>
-      <c r="K17">
+      <c r="L17">
         <v>147.62379999999999</v>
       </c>
-      <c r="L17">
-        <v>0</v>
-      </c>
       <c r="M17">
+        <v>0</v>
+      </c>
+      <c r="N17">
         <v>15</v>
       </c>
-      <c r="N17">
-        <v>0</v>
-      </c>
       <c r="O17">
+        <v>0</v>
+      </c>
+      <c r="P17">
         <v>1E-4</v>
       </c>
-      <c r="P17">
+      <c r="Q17">
         <v>0.1476238</v>
       </c>
-      <c r="Q17">
-        <v>0</v>
-      </c>
       <c r="R17">
-        <f t="shared" si="1"/>
-        <v>14.8523762</v>
+        <v>0</v>
       </c>
       <c r="S17">
         <v>14.8523762</v>
@@ -2135,52 +2163,55 @@
         <v>733.84551438999995</v>
       </c>
       <c r="V17" t="s">
-        <v>45</v>
+        <v>57</v>
       </c>
       <c r="W17" t="s">
-        <v>46</v>
+        <v>58</v>
+      </c>
+      <c r="X17" t="s">
+        <v>44</v>
       </c>
     </row>
-    <row r="18" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>70979512</v>
       </c>
-      <c r="B18" s="1">
+      <c r="B18">
+        <v>1746602409577680</v>
+      </c>
+      <c r="C18" s="1">
         <v>45784.305659722224</v>
       </c>
-      <c r="C18" t="s">
-        <v>29</v>
-      </c>
       <c r="D18" t="s">
-        <v>30</v>
+        <v>39</v>
       </c>
       <c r="E18" t="s">
-        <v>47</v>
-      </c>
-      <c r="F18">
+        <v>40</v>
+      </c>
+      <c r="F18" t="s">
+        <v>59</v>
+      </c>
+      <c r="G18">
         <v>733.16</v>
       </c>
-      <c r="H18">
-        <v>0</v>
-      </c>
       <c r="I18">
+        <v>0</v>
+      </c>
+      <c r="J18">
         <v>1832.9</v>
-      </c>
-      <c r="J18">
-        <v>1833.1452999999999</v>
       </c>
       <c r="K18">
         <v>1833.1452999999999</v>
       </c>
       <c r="L18">
-        <v>0</v>
+        <v>1833.1452999999999</v>
       </c>
       <c r="M18">
+        <v>0</v>
+      </c>
+      <c r="N18">
         <v>733.16</v>
       </c>
-      <c r="N18">
-        <v>0</v>
-      </c>
       <c r="O18">
         <v>0</v>
       </c>
@@ -2191,8 +2222,7 @@
         <v>0</v>
       </c>
       <c r="R18">
-        <f t="shared" si="1"/>
-        <v>733.16</v>
+        <v>0</v>
       </c>
       <c r="S18">
         <v>733.16</v>
@@ -2204,10 +2234,13 @@
         <v>733.16</v>
       </c>
       <c r="V18" t="s">
-        <v>48</v>
+        <v>60</v>
       </c>
       <c r="W18" t="s">
-        <v>49</v>
+        <v>61</v>
+      </c>
+      <c r="X18" t="s">
+        <v>44</v>
       </c>
     </row>
   </sheetData>
